--- a/report_forms/040_data_integrity_compliance_report_form--report_forms.xlsx
+++ b/report_forms/040_data_integrity_compliance_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'data_loss'}</t>
+          <t>data_loss</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Data Loss'}</t>
+          <t>Data Loss</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'security_breach'}</t>
+          <t>security_breach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Security Breach'}</t>
+          <t>Security Breach</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'policy_violation'}</t>
+          <t>policy_violation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Policy Violation'}</t>
+          <t>Policy Violation</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'security'}</t>
+          <t>security</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Security'}</t>
+          <t>Security</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'compliance_team'}</t>
+          <t>compliance_team</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Compliance Team'}</t>
+          <t>Compliance Team</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'bob_smith'}</t>
+          <t>bob_smith</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Smith'}</t>
+          <t>Bob Smith</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'john_smith'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'John Smith'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'jane_smith'}</t>
+          <t>jane_smith</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Smith'}</t>
+          <t>Jane Smith</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'bob_johnson'}</t>
+          <t>bob_johnson</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Bob Johnson'}</t>
+          <t>Bob Johnson</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'data_loss'}</t>
+          <t>data_loss</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Data Loss'}</t>
+          <t>Data Loss</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'security_breach'}</t>
+          <t>security_breach</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Security Breach'}</t>
+          <t>Security Breach</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'policy_violation'}</t>
+          <t>policy_violation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Policy Violation'}</t>
+          <t>Policy Violation</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
